--- a/outputs/marketing/auditoria/Alvos_Aquisicao.xlsx
+++ b/outputs/marketing/auditoria/Alvos_Aquisicao.xlsx
@@ -11716,10 +11716,10 @@
         </is>
       </c>
       <c r="K142" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
@@ -15364,10 +15364,10 @@
         </is>
       </c>
       <c r="K190" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L190" s="2" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
@@ -19620,10 +19620,10 @@
         </is>
       </c>
       <c r="K246" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L246" s="2" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="M246" s="2" t="inlineStr">
         <is>
